--- a/data/trans_orig/P04B3_1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106618</t>
+          <t>107254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>144962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84320</t>
+          <t>84939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127778</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203043</t>
+          <t>203587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>264513</t>
+          <t>262393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>59170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91057</t>
+          <t>90915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57963</t>
+          <t>58146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90057</t>
+          <t>89837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127017</t>
+          <t>125908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172793</t>
+          <t>172781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50796</t>
+          <t>51489</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87386</t>
+          <t>87834</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54267</t>
+          <t>56606</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86853</t>
+          <t>86871</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117082</t>
+          <t>114409</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165564</t>
+          <t>165809</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>344136</t>
+          <t>340639</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>394312</t>
+          <t>394197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>441071</t>
+          <t>441797</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>526810</t>
+          <t>522446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>797792</t>
+          <t>800588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>900333</t>
+          <t>907169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128218</t>
+          <t>115015</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>315284</t>
+          <t>314408</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>228702</t>
+          <t>226680</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>273028</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>318660</t>
+          <t>327433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>566462</t>
+          <t>569794</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62098</t>
+          <t>59939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167395</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109661</t>
+          <t>108605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145356</t>
+          <t>144200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169227</t>
+          <t>169881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292993</t>
+          <t>290337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95652</t>
+          <t>81218</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>220501</t>
+          <t>223076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137121</t>
+          <t>136827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177125</t>
+          <t>175514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207793</t>
+          <t>212228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>374230</t>
+          <t>375668</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>513515</t>
+          <t>514086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>903322</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>400249</t>
+          <t>400911</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>453057</t>
+          <t>454213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>944411</t>
+          <t>938408</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1443874</t>
+          <t>1436539</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>86425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126425</t>
+          <t>124055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49480</t>
+          <t>48136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134339</t>
+          <t>135202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129506</t>
+          <t>122142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242490</t>
+          <t>245729</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75821</t>
+          <t>76049</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115772</t>
+          <t>116153</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>45314</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126431</t>
+          <t>125176</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>124264</t>
+          <t>127569</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>222031</t>
+          <t>223076</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>180632</t>
+          <t>179441</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239469</t>
+          <t>238573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95698</t>
+          <t>85805</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242082</t>
+          <t>240950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254693</t>
+          <t>239134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>458943</t>
+          <t>459332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>264671</t>
+          <t>267854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>327833</t>
+          <t>330612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>440532</t>
+          <t>440059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>738219</t>
+          <t>756247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>728722</t>
+          <t>728800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1114083</t>
+          <t>1169014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>273596</t>
+          <t>274652</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>333395</t>
+          <t>334956</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>350070</t>
+          <t>348223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>563140</t>
+          <t>548224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>648099</t>
+          <t>640764</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>866576</t>
+          <t>876519</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105357</t>
+          <t>105930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151933</t>
+          <t>149872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132665</t>
+          <t>131046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188427</t>
+          <t>190681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>258222</t>
+          <t>253863</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>327299</t>
+          <t>325768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>99951</t>
+          <t>101038</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>142198</t>
+          <t>144464</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>109383</t>
+          <t>107804</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160014</t>
+          <t>158210</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>221898</t>
+          <t>223894</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>290565</t>
+          <t>289474</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>345952</t>
+          <t>344898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>411572</t>
+          <t>410230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>304728</t>
+          <t>313298</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>423978</t>
+          <t>425596</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>679191</t>
+          <t>684534</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>812932</t>
+          <t>815145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>604346</t>
+          <t>588431</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>851570</t>
+          <t>845529</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>728939</t>
+          <t>725657</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1027691</t>
+          <t>1024724</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1453880</t>
+          <t>1443795</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1823570</t>
+          <t>1813152</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>330629</t>
+          <t>322515</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>468030</t>
+          <t>467180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>376428</t>
+          <t>375967</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>511697</t>
+          <t>506125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>765267</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>952842</t>
+          <t>954378</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>444993</t>
+          <t>436694</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>630534</t>
+          <t>628065</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>443065</t>
+          <t>453259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>599033</t>
+          <t>602186</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>960290</t>
+          <t>945840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1197337</t>
+          <t>1201885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1550481</t>
+          <t>1557268</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2082784</t>
+          <t>2111323</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1692402</t>
+          <t>1699710</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2175886</t>
+          <t>2208275</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3319354</t>
+          <t>3302257</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4013669</t>
+          <t>4029371</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Habitat-trans_orig.xlsx
@@ -725,67 +725,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>125015</t>
+          <t>141403</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107254</t>
+          <t>121283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144962</t>
+          <t>164812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>123909</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>109417</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>143005</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>16,88%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>110425</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>84939</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>128420</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,22%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>235440</t>
+          <t>265312</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203587</t>
+          <t>239195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262393</t>
+          <t>296161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>84857</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59170</t>
+          <t>69008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90915</t>
+          <t>102774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74987</t>
+          <t>83256</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58146</t>
+          <t>70637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89837</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>149561</t>
+          <t>168113</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125908</t>
+          <t>145033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172781</t>
+          <t>190843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66561</t>
+          <t>68650</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51489</t>
+          <t>53288</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87834</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71479</t>
+          <t>81966</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56606</t>
+          <t>69260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86871</t>
+          <t>97501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>150615</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114409</t>
+          <t>129691</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165809</t>
+          <t>174422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>369291</t>
+          <t>395800</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>340639</t>
+          <t>367443</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>394197</t>
+          <t>423541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>468440</t>
+          <t>445049</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>441797</t>
+          <t>422891</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>522446</t>
+          <t>465069</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>837732</t>
+          <t>840848</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>800588</t>
+          <t>805300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>907169</t>
+          <t>876638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>239846</t>
+          <t>280594</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115015</t>
+          <t>249965</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>314408</t>
+          <t>312959</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>249987</t>
+          <t>286634</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>226680</t>
+          <t>260833</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>272942</t>
+          <t>312500</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>489833</t>
+          <t>567228</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>327433</t>
+          <t>522162</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>569794</t>
+          <t>606935</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>122981</t>
+          <t>137719</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59939</t>
+          <t>117108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163935</t>
+          <t>164727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>124907</t>
+          <t>144440</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108605</t>
+          <t>125612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144200</t>
+          <t>166080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>247889</t>
+          <t>282159</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169881</t>
+          <t>251971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290337</t>
+          <t>313673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>164122</t>
+          <t>178137</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81218</t>
+          <t>151857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>223076</t>
+          <t>209401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>156188</t>
+          <t>171510</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136827</t>
+          <t>150767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175514</t>
+          <t>194794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>320310</t>
+          <t>349647</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212228</t>
+          <t>313791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>375668</t>
+          <t>387745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>665914</t>
+          <t>452467</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>514086</t>
+          <t>419950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>934729</t>
+          <t>491064</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>426788</t>
+          <t>467214</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>400911</t>
+          <t>435439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>454213</t>
+          <t>497021</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1092702</t>
+          <t>919682</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>938408</t>
+          <t>876662</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1436539</t>
+          <t>971667</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>957870</t>
+          <t>1069798</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957870</t>
+          <t>1069798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957870</t>
+          <t>1069798</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2150734</t>
+          <t>2118715</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150734</t>
+          <t>2118715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2150734</t>
+          <t>2118715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>105007</t>
+          <t>120062</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86425</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124055</t>
+          <t>143941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>99137</t>
+          <t>118986</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48136</t>
+          <t>99958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135202</t>
+          <t>137608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>204144</t>
+          <t>239049</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122142</t>
+          <t>209916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245729</t>
+          <t>269924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93734</t>
+          <t>107858</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76049</t>
+          <t>88284</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>116153</t>
+          <t>129367</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91926</t>
+          <t>119705</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45314</t>
+          <t>103172</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125176</t>
+          <t>140073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>185659</t>
+          <t>227563</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>127569</t>
+          <t>199994</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>223076</t>
+          <t>256706</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>208861</t>
+          <t>232339</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>179441</t>
+          <t>201728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>238573</t>
+          <t>263258</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>178925</t>
+          <t>210023</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85805</t>
+          <t>186903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240950</t>
+          <t>234786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>387786</t>
+          <t>442362</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>239134</t>
+          <t>406406</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459332</t>
+          <t>483761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>296914</t>
+          <t>341636</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267854</t>
+          <t>310812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330612</t>
+          <t>376759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>562722</t>
+          <t>362838</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>440059</t>
+          <t>337133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>756247</t>
+          <t>392254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>859636</t>
+          <t>704474</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>728800</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1169014</t>
+          <t>747687</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>302113</t>
+          <t>348834</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>274652</t>
+          <t>317628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>334956</t>
+          <t>382267</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>405007</t>
+          <t>382279</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>348223</t>
+          <t>356090</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>548224</t>
+          <t>412933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>707121</t>
+          <t>731112</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>640764</t>
+          <t>690053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>876519</t>
+          <t>775878</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>137260</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105930</t>
+          <t>116774</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149872</t>
+          <t>166770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>164934</t>
+          <t>181223</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131046</t>
+          <t>160472</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>190681</t>
+          <t>204810</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>291009</t>
+          <t>318483</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253863</t>
+          <t>286283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>325768</t>
+          <t>349061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119588</t>
+          <t>123360</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>101038</t>
+          <t>102761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>144464</t>
+          <t>145889</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>136693</t>
+          <t>150543</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107804</t>
+          <t>132374</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>158210</t>
+          <t>172090</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>256281</t>
+          <t>273903</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>223894</t>
+          <t>243764</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>289474</t>
+          <t>303133</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>377873</t>
+          <t>377986</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>344898</t>
+          <t>342864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>410230</t>
+          <t>408083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>387409</t>
+          <t>403275</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>313298</t>
+          <t>372964</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>425596</t>
+          <t>432212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>765282</t>
+          <t>781261</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>684534</t>
+          <t>739490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>815145</t>
+          <t>825146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>925650</t>
+          <t>987440</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>925650</t>
+          <t>987440</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>925650</t>
+          <t>987440</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1094043</t>
+          <t>1117320</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1094043</t>
+          <t>1117320</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1094043</t>
+          <t>1117320</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2019693</t>
+          <t>2104760</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2019693</t>
+          <t>2104760</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2019693</t>
+          <t>2104760</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>771982</t>
+          <t>890893</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>588431</t>
+          <t>835357</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>845529</t>
+          <t>945890</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>864557</t>
+          <t>911808</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>725657</t>
+          <t>867532</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1024724</t>
+          <t>962139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1636539</t>
+          <t>1802701</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1443795</t>
+          <t>1729854</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1813152</t>
+          <t>1877262</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>417364</t>
+          <t>467694</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322515</t>
+          <t>430453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>467180</t>
+          <t>514399</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>456754</t>
+          <t>528624</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>375967</t>
+          <t>492896</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>506125</t>
+          <t>573172</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>874117</t>
+          <t>996318</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>765267</t>
+          <t>947408</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>954378</t>
+          <t>1055853</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>559132</t>
+          <t>602486</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>436694</t>
+          <t>553874</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>628065</t>
+          <t>654311</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>543285</t>
+          <t>614041</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>453259</t>
+          <t>575851</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>602186</t>
+          <t>651834</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1102417</t>
+          <t>1216527</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>945840</t>
+          <t>1154464</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1201885</t>
+          <t>1281494</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1709993</t>
+          <t>1567890</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1557268</t>
+          <t>1507148</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2111323</t>
+          <t>1640260</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,67 +3375,67 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1845359</t>
+          <t>1678376</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1699710</t>
+          <t>1618982</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2208275</t>
+          <t>1734949</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>46,48%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>3246266</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>3163163</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>3326446</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>45,81%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>59,52%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>4031</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>3555352</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>3302257</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>4029371</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>49,6%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3458471</t>
+          <t>3528962</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3709954</t>
+          <t>3732849</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7168425</t>
+          <t>7261812</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
